--- a/ValueSet-mii-vs-person-icd10who.xlsx
+++ b/ValueSet-mii-vs-person-icd10who.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2026.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-08</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>Define ICD-10-WHO codes allowed for cause of death representation.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -355,22 +358,24 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -389,28 +394,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -429,28 +434,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -469,28 +474,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -509,28 +514,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-mii-vs-person-icd10who.xlsx
+++ b/ValueSet-mii-vs-person-icd10who.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-person-icd10who.xlsx
+++ b/ValueSet-mii-vs-person-icd10who.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
